--- a/output/pdf_financials_xlsx/GPIN.xlsx
+++ b/output/pdf_financials_xlsx/GPIN.xlsx
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.951055</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.359324</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.10466</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.121993</v>
       </c>
     </row>
     <row r="93">
@@ -2390,7 +2390,7 @@
         <v>0.7932979999999999</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.337714</v>
+        <v>-0.337714</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.269018</v>
@@ -3536,7 +3536,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5310,7 +5314,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -5934,7 +5942,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>2.951055</v>
       </c>
@@ -6022,7 +6034,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.337714</v>
+        <v>-0.337714</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>-0.269018</v>

--- a/output/pdf_financials_xlsx/GPIN.xlsx
+++ b/output/pdf_financials_xlsx/GPIN.xlsx
@@ -664,10 +664,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.051074</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.047343</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         <v>-7.11412</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.7932979999999999</v>
+        <v>0.742224</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.337714</v>
+        <v>0.290371</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         <v>-6.97839</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.7942129999999999</v>
+        <v>0.743139</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.337714</v>
+        <v>0.290371</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.912806</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.613412</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.213927</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.081139</v>
       </c>
     </row>
     <row r="35">
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.912806</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.613412</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.213927</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.081139</v>
       </c>
     </row>
     <row r="37">
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.573678</v>
+        <v>0.660872</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.741562</v>
+        <v>2.12815</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.276364</v>
+        <v>2.062437</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">

--- a/output/pdf_financials_xlsx/GPIN.xlsx
+++ b/output/pdf_financials_xlsx/GPIN.xlsx
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.13573</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.000915</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -8266,7 +8266,11 @@
           <t>Proceeds from disposals of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
         <v>0.75</v>
       </c>
@@ -8692,7 +8696,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10106,7 +10110,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">

--- a/output/pdf_financials_xlsx/GPIN.xlsx
+++ b/output/pdf_financials_xlsx/GPIN.xlsx
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.44765</v>
+        <v>0.50465</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.210806</v>
+        <v>0.240806</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.056437</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.44765</v>
+        <v>0.50465</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.210806</v>
+        <v>0.240806</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.056437</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.7278250000000001</v>
+        <v>0.670825</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-7.11412</v>
+        <v>-7.137776</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.7932979999999999</v>
+        <v>0.816954</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.337714</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.023656</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.023656</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-2.812012</v>
+        <v>-4.302108</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.232735</v>
+        <v>-0.439437</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.232735</v>
+        <v>-0.204109</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-2.812012</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>1.232735</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>0.5418230000000001</v>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.11412</v>
+        <v>-7.137776</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.742224</v>
+        <v>0.76588</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.290371</v>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.97839</v>
+        <v>-7.002046</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.743139</v>
+        <v>0.766795</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.290371</v>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-593.6655394627704</v>
+        <v>-595.6780025096238</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3314197587595912</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>2.895634270717813</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.113702</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.097438</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.02947</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.10611</v>
       </c>
     </row>
     <row r="68">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-7.11412</v>
+        <v>-4.302108</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>0.7932979999999999</v>
@@ -3083,10 +3083,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.817216</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>0.742337</v>
@@ -6090,7 +6088,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -7734,7 +7736,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-4.302108</v>
       </c>
@@ -8232,7 +8238,11 @@
           <t>Cash generated from (used in) in operating activities</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
         <v>-1.817216</v>
       </c>
@@ -8772,7 +8782,11 @@
           <t>Director fees 11</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -9228,7 +9242,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -9264,7 +9282,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -9298,7 +9320,11 @@
           <t>Net income from discontinued operations 12</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -9718,7 +9744,11 @@
           <t>Net loss from continuing operations - - - - -</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -10000,11 +10030,7 @@
           <t>Net income from discontinuing operations - - - - -</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -10184,7 +10210,11 @@
           <t>Director fees 16</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E198" s="5" t="n">
         <v>0.057</v>
       </c>
@@ -10646,7 +10676,11 @@
           <t>Current income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E211" s="5" t="n">
         <v>-0.023656</v>
       </c>
@@ -10680,7 +10714,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E212" s="5" t="n">
         <v>-4.302108</v>
       </c>
@@ -10716,7 +10754,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
@@ -11406,7 +11444,11 @@
           <t>Net income from discontinued operations - - - - - 1,232,735 1,232,735</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>1.232735</v>
       </c>
